--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
   <si>
-    <t xml:space="preserve">SkillId</t>
+    <t xml:space="preserve">SkillTid</t>
   </si>
   <si>
     <t xml:space="preserve">SkillName</t>
@@ -52,7 +52,82 @@
     <t xml:space="preserve">N회 콤보 공격</t>
   </si>
   <si>
-    <t xml:space="preserve">1,2,3</t>
+    <t xml:space="preserve">강공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회피</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구르기</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복 물약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">불 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최대 n회 스택, 스택에 따라 특수효과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">얼음 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">무속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대미지 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">화염 특수공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특수 공격 추가, 스택이 쌓인 적 폭발</t>
+  </si>
+  <si>
+    <t xml:space="preserve">얼음 속성 강공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격 적중 시 스택 폭발</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격 속도 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마지막 타격 대미지 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회피 스킬을 대시로 변경</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대시 연계공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스태미나 최대치 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스태미나 회복 속도 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가드 피해 감소율 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복량 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복 물약 개수 증가</t>
   </si>
 </sst>
 </file>
@@ -64,8 +139,8 @@
   </numFmts>
   <fonts count="6">
     <font>
-      <sz val="10"/>
-      <name val="나눔고딕"/>
+      <sz val="9"/>
+      <name val="맑은 고딕 Semilight"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -87,19 +162,19 @@
     <font>
       <sz val="9"/>
       <color theme="0"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,6 +185,12 @@
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.3499"/>
         <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,9 +235,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -167,7 +252,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -176,7 +261,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -204,7 +289,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFCCCCCC"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -362,94 +447,375 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="12.67"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I1" s="2"/>
+      <c r="B1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4"/>
+      <c r="I2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -46,88 +46,22 @@
     <t xml:space="preserve">NeededSkillPoint</t>
   </si>
   <si>
+    <t xml:space="preserve">IconPathString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PositionX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PositionY</t>
+  </si>
+  <si>
     <t xml:space="preserve">일반 공격</t>
   </si>
   <si>
     <t xml:space="preserve">N회 콤보 공격</t>
   </si>
   <si>
-    <t xml:space="preserve">강공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회피</t>
-  </si>
-  <si>
-    <t xml:space="preserve">구르기</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회복 물약</t>
-  </si>
-  <si>
-    <t xml:space="preserve">불 속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최대 n회 스택, 스택에 따라 특수효과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">얼음 속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">무속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대미지 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 특수공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특수 공격 추가, 스택이 쌓인 적 폭발</t>
-  </si>
-  <si>
-    <t xml:space="preserve">얼음 속성 강공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">강공격 적중 시 스택 폭발</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 속도 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마지막 타격 대미지 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대시</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회피 스킬을 대시로 변경</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대시 연계공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">스태미나 최대치 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3, 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">스태미나 회복 속도 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가드 피해 감소율 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회복량 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회복 물약 개수 증가</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
   </si>
 </sst>
 </file>
@@ -235,20 +169,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -447,7 +377,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="12.67"/>
@@ -482,340 +412,139 @@
       <c r="H1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I1" s="3"/>
+      <c r="I1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5"/>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="n">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="n">
+        <v>3333</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="B17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="B18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="B19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="B21" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -62,6 +62,15 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">일반 공격2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NNNN회 콤보 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boost-_18_.Img_Healing-Boost-_18_</t>
   </si>
 </sst>
 </file>
@@ -484,16 +493,34 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
+      <c r="B4" s="4" t="n">
+        <v>3334</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boost-_18_.Img_Healing-Boost-_18_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASDFCVXZ</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,27 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>3334</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve">ASDFCVXZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">asdf</t>
   </si>
 </sst>
 </file>
@@ -552,10 +555,47 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4"/>
+      <c r="B6" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>231</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>1234</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4"/>
+      <c r="B7" s="4" t="n">
+        <v>4123</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -58,28 +58,139 @@
     <t xml:space="preserve">일반 공격</t>
   </si>
   <si>
-    <t xml:space="preserve">N회 콤보 공격</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Normal-Attack-Icon-_1_.Img_Normal-Attack-Icon-_1_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Heavy-Attack-Icon-_2_.Img_Heavy-Attack-Icon-_2_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회피</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Dodge-Icon-_3_.Img_Dodge-Icon-_3_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Guard-Icon-_4_.Img_Guard-Icon-_4_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복 물약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Greater-Potion-_5_.Img_Greater-Potion-_5_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">불 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_fire-enchant-_6_.Img_fire-enchant-_6_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">얼음 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_ice-enchant-_7_.Img_ice-enchant-_7_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그냥 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_No-enchant-_8_.Img_No-enchant-_8_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특수공격 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Homing-Burst-_9_.Img_Homing-Burst-_9_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_enhanced-heavy-attack-_10_.Img_enhanced-heavy-attack-_10_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격속도 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Attack-Speed-Up-Icon-_11_.Img_Attack-Speed-Up-Icon-_11_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마지막 타격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Final-Strike_Icon-_12_.Img_Final-Strike_Icon-_12_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대시</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Invincible-Dash-_13_.Img_Invincible-Dash-_13_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대시 연계 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Whirlwind-Strike-_14_.Img_Whirlwind-Strike-_14_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스태미나 최대치 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Max-Stamina-Icon-_15_.Img_Max-Stamina-Icon-_15_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스태미나 회복 속도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Stamina-Recovery-Icon-_16_.Img_Stamina-Recovery-Icon-_16_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 감소율 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Damage-Reduction-Icon-_17_.Img_Damage-Reduction-Icon-_17_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복량 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boost-_18_.Img_Healing-Boost-_18_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">물약 개수 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boosts_19_.Img_Healing-Boosts_19_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연계 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_normal-attack+-heavy-attack.Img_normal-attack+-heavy-attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차징 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,20</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">일반 공격2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NNNN회 콤보 공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boost-_18_.Img_Healing-Boost-_18_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASDFCVXZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asdf</t>
   </si>
 </sst>
 </file>
@@ -395,7 +506,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="12.67"/>
@@ -473,17 +584,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="n">
-        <v>3333</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="5"/>
       <c r="G3" s="4" t="n">
@@ -493,26 +602,24 @@
         <v>0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="n">
-        <v>3334</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="5"/>
       <c r="G4" s="4" t="n">
@@ -522,122 +629,463 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="n">
-        <v>1234</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>3334</v>
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="J5" s="1" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>400</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>231</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>1234</v>
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="J6" s="1" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="K6" s="1" t="n">
-        <v>600</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="n">
-        <v>4123</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>213</v>
-      </c>
-      <c r="E7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="K7" s="1" t="n">
+      <c r="E13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="K14" s="1" t="n">
         <v>600</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4"/>
-    </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4"/>
+      <c r="B15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4"/>
+      <c r="B16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4"/>
+      <c r="B17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>1050</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4"/>
+      <c r="B18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>1050</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4"/>
+      <c r="B19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4"/>
+      <c r="B20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4"/>
+      <c r="B21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>350</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -46,88 +46,151 @@
     <t xml:space="preserve">NeededSkillPoint</t>
   </si>
   <si>
+    <t xml:space="preserve">IconPathString</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PositionX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PositionY</t>
+  </si>
+  <si>
     <t xml:space="preserve">일반 공격</t>
   </si>
   <si>
-    <t xml:space="preserve">N회 콤보 공격</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Normal-Attack-Icon-_1_.Img_Normal-Attack-Icon-_1_</t>
   </si>
   <si>
     <t xml:space="preserve">강공격</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Heavy-Attack-Icon-_2_.Img_Heavy-Attack-Icon-_2_</t>
+  </si>
+  <si>
     <t xml:space="preserve">회피</t>
   </si>
   <si>
-    <t xml:space="preserve">구르기</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Dodge-Icon-_3_.Img_Dodge-Icon-_3_</t>
   </si>
   <si>
     <t xml:space="preserve">가드</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Guard-Icon-_4_.Img_Guard-Icon-_4_</t>
+  </si>
+  <si>
     <t xml:space="preserve">회복 물약</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Greater-Potion-_5_.Img_Greater-Potion-_5_</t>
+  </si>
+  <si>
     <t xml:space="preserve">불 속성 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">최대 n회 스택, 스택에 따라 특수효과</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_fire-enchant-_6_.Img_fire-enchant-_6_</t>
   </si>
   <si>
     <t xml:space="preserve">얼음 속성 강화</t>
   </si>
   <si>
-    <t xml:space="preserve">무속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대미지 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화염 특수공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특수 공격 추가, 스택이 쌓인 적 폭발</t>
-  </si>
-  <si>
-    <t xml:space="preserve">얼음 속성 강공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">강공격 적중 시 스택 폭발</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2, 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공격 속도 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">마지막 타격 대미지 증가</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_ice-enchant-_7_.Img_ice-enchant-_7_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">그냥 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_No-enchant-_8_.Img_No-enchant-_8_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특수공격 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Homing-Burst-_9_.Img_Homing-Burst-_9_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_enhanced-heavy-attack-_10_.Img_enhanced-heavy-attack-_10_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공격속도 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Attack-Speed-Up-Icon-_11_.Img_Attack-Speed-Up-Icon-_11_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">마지막 타격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Final-Strike_Icon-_12_.Img_Final-Strike_Icon-_12_</t>
   </si>
   <si>
     <t xml:space="preserve">대시</t>
   </si>
   <si>
-    <t xml:space="preserve">회피 스킬을 대시로 변경</t>
-  </si>
-  <si>
-    <t xml:space="preserve">대시 연계공격</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Invincible-Dash-_13_.Img_Invincible-Dash-_13_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대시 연계 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Whirlwind-Strike-_14_.Img_Whirlwind-Strike-_14_</t>
   </si>
   <si>
     <t xml:space="preserve">스태미나 최대치 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">3, 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">스태미나 회복 속도 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가드 피해 감소율 증가</t>
+    <t xml:space="preserve">3,4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Max-Stamina-Icon-_15_.Img_Max-Stamina-Icon-_15_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">스태미나 회복 속도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Stamina-Recovery-Icon-_16_.Img_Stamina-Recovery-Icon-_16_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">피해 감소율 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Damage-Reduction-Icon-_17_.Img_Damage-Reduction-Icon-_17_</t>
   </si>
   <si>
     <t xml:space="preserve">회복량 증가</t>
   </si>
   <si>
-    <t xml:space="preserve">회복 물약 개수 증가</t>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boost-_18_.Img_Healing-Boost-_18_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">물약 개수 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boosts_19_.Img_Healing-Boosts_19_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연계 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_normal-attack+-heavy-attack.Img_normal-attack+-heavy-attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">차징 공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
   </si>
 </sst>
 </file>
@@ -235,20 +298,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -447,7 +506,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="12.67"/>
@@ -482,82 +541,109 @@
       <c r="H1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="I1" s="3"/>
+      <c r="I1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="I2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="J2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5" t="n">
+      <c r="K2" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="5"/>
+      <c r="I3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5" t="n">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5" t="n">
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
@@ -565,13 +651,22 @@
       <c r="H5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>900</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1</v>
@@ -579,13 +674,22 @@
       <c r="H6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
@@ -593,76 +697,100 @@
       <c r="H7" s="1" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="n">
+      <c r="I7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="n">
+      <c r="I8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H10" s="1" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="n">
+      <c r="I10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>6</v>
@@ -670,44 +798,68 @@
       <c r="H11" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>420</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>11</v>
@@ -715,30 +867,45 @@
       <c r="H14" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>600</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>3</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="4" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>13</v>
@@ -746,55 +913,91 @@
       <c r="H16" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>750</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>1050</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>500</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>15</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>1050</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>750</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="n">
+      <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>5</v>
@@ -802,13 +1005,22 @@
       <c r="H20" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="n">
+      <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>5</v>
@@ -816,6 +1028,64 @@
       <c r="H21" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I21" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>450</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>350</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -28,16 +28,16 @@
     <t xml:space="preserve">SkillTid</t>
   </si>
   <si>
-    <t xml:space="preserve">SkillName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
+    <t xml:space="preserve">설명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TextTid</t>
   </si>
   <si>
     <t xml:space="preserve">Prerequisites</t>
   </si>
   <si>
-    <t xml:space="preserve">ExclusiveGroupId</t>
+    <t xml:space="preserve">ExclusiveSkills</t>
   </si>
   <si>
     <t xml:space="preserve">bIsDefaultSkill</t>
@@ -88,16 +88,25 @@
     <t xml:space="preserve">불 속성 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">7,8</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_fire-enchant-_6_.Img_fire-enchant-_6_</t>
   </si>
   <si>
     <t xml:space="preserve">얼음 속성 강화</t>
   </si>
   <si>
+    <t xml:space="preserve">6,8</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_ice-enchant-_7_.Img_ice-enchant-_7_</t>
   </si>
   <si>
     <t xml:space="preserve">그냥 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,7</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_No-enchant-_8_.Img_No-enchant-_8_</t>
@@ -298,7 +307,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -321,6 +330,10 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -509,7 +522,9 @@
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.81"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.91"/>
@@ -524,7 +539,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1" s="2" t="n">
         <v>1</v>
@@ -592,7 +607,9 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4" t="n">
+        <v>33001</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="5"/>
       <c r="G3" s="4" t="n">
@@ -619,7 +636,9 @@
       <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4" t="n">
+        <v>33002</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5"/>
       <c r="G4" s="4" t="n">
@@ -645,6 +664,9 @@
       <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="D5" s="1" t="n">
+        <v>33003</v>
+      </c>
       <c r="G5" s="1" t="n">
         <v>1</v>
       </c>
@@ -668,6 +690,9 @@
       <c r="C6" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D6" s="4" t="n">
+        <v>33004</v>
+      </c>
       <c r="G6" s="1" t="n">
         <v>1</v>
       </c>
@@ -691,6 +716,9 @@
       <c r="C7" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D7" s="4" t="n">
+        <v>33005</v>
+      </c>
       <c r="G7" s="1" t="n">
         <v>1</v>
       </c>
@@ -714,17 +742,20 @@
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D8" s="1" t="n">
+        <v>33006</v>
+      </c>
       <c r="E8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>18</v>
+      <c r="F8" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>180</v>
@@ -738,19 +769,22 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>33007</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>18</v>
+      <c r="F9" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>300</v>
@@ -764,19 +798,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>33008</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>18</v>
+      <c r="F10" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>420</v>
@@ -790,7 +827,10 @@
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>33009</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>6</v>
@@ -799,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>180</v>
@@ -813,16 +853,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>33010</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>450</v>
@@ -836,7 +879,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>33011</v>
       </c>
       <c r="E13" s="1" t="n">
         <v>1</v>
@@ -845,7 +891,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>120</v>
@@ -859,7 +905,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>33012</v>
       </c>
       <c r="E14" s="1" t="n">
         <v>11</v>
@@ -868,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>120</v>
@@ -882,7 +931,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>33013</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>3</v>
@@ -891,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>700</v>
@@ -905,7 +957,10 @@
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>33014</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>13</v>
@@ -914,7 +969,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>700</v>
@@ -928,16 +983,19 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>33015</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>1050</v>
@@ -951,7 +1009,10 @@
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>33016</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>15</v>
@@ -960,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>1050</v>
@@ -974,7 +1035,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>33017</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>4</v>
@@ -983,7 +1047,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>1200</v>
@@ -997,7 +1061,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>33018</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>5</v>
@@ -1006,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>1400</v>
@@ -1020,7 +1087,10 @@
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>33019</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>5</v>
@@ -1028,8 +1098,8 @@
       <c r="H21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="0" t="s">
-        <v>50</v>
+      <c r="I21" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>1600</v>
@@ -1043,16 +1113,19 @@
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>33020</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>450</v>
@@ -1066,16 +1139,19 @@
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>33021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>350</v>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -55,12 +55,18 @@
     <t xml:space="preserve">PositionY</t>
   </si>
   <si>
+    <t xml:space="preserve">구현됨?</t>
+  </si>
+  <si>
     <t xml:space="preserve">일반 공격</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Normal-Attack-Icon-_1_.Img_Normal-Attack-Icon-_1_</t>
   </si>
   <si>
+    <t xml:space="preserve">기본 스킬</t>
+  </si>
+  <si>
     <t xml:space="preserve">강공격</t>
   </si>
   <si>
@@ -94,6 +100,9 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_fire-enchant-_6_.Img_fire-enchant-_6_</t>
   </si>
   <si>
+    <t xml:space="preserve">CombatComponent</t>
+  </si>
+  <si>
     <t xml:space="preserve">얼음 속성 강화</t>
   </si>
   <si>
@@ -118,6 +127,9 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Homing-Burst-_9_.Img_Homing-Burst-_9_</t>
   </si>
   <si>
+    <t xml:space="preserve">PlayerCharacter</t>
+  </si>
+  <si>
     <t xml:space="preserve">강공격 강화</t>
   </si>
   <si>
@@ -133,6 +145,9 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Attack-Speed-Up-Icon-_11_.Img_Attack-Speed-Up-Icon-_11_</t>
   </si>
   <si>
+    <t xml:space="preserve">StatComponent</t>
+  </si>
+  <si>
     <t xml:space="preserve">마지막 타격</t>
   </si>
   <si>
@@ -145,6 +160,9 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Invincible-Dash-_13_.Img_Invincible-Dash-_13_</t>
   </si>
   <si>
+    <t xml:space="preserve">ActionComponent</t>
+  </si>
+  <si>
     <t xml:space="preserve">대시 연계 공격</t>
   </si>
   <si>
@@ -176,6 +194,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Healing-Boost-_18_.Img_Healing-Boost-_18_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아직 없음</t>
   </si>
   <si>
     <t xml:space="preserve">물약 개수 증가</t>
@@ -209,7 +230,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="9"/>
       <name val="맑은 고딕 Semilight"/>
@@ -245,8 +266,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,7 +288,43 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F2A1"/>
+        <bgColor rgb="FFFFFFA6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFDBB6"/>
+        <bgColor rgb="FFFFD7D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEE6EF"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7D7"/>
+        <bgColor rgb="FFFFDBB6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFA6"/>
+        <bgColor rgb="FFE8F2A1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFDEE6EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,7 +369,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -330,6 +392,30 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -365,12 +451,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE8F2A1"/>
+      <rgbColor rgb="FFDEE6EF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -381,12 +467,12 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFD7D7"/>
+      <rgbColor rgb="FFFFFFA6"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFDBB6"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -519,7 +605,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.67"/>
@@ -528,7 +614,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.81"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="30.25"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -565,6 +653,12 @@
       <c r="K1" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="L1" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
@@ -598,6 +692,9 @@
       <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="M2" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
@@ -605,7 +702,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="4" t="n">
         <v>33001</v>
@@ -619,13 +716,16 @@
         <v>0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>300</v>
       </c>
       <c r="K3" s="1" t="n">
         <v>250</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,7 +734,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>33002</v>
@@ -648,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>600</v>
@@ -656,13 +756,14 @@
       <c r="K4" s="1" t="n">
         <v>250</v>
       </c>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>33003</v>
@@ -674,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>900</v>
@@ -682,13 +783,14 @@
       <c r="K5" s="1" t="n">
         <v>250</v>
       </c>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>33004</v>
@@ -700,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>1200</v>
@@ -708,13 +810,14 @@
       <c r="K6" s="1" t="n">
         <v>250</v>
       </c>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>33005</v>
@@ -726,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>1500</v>
@@ -734,13 +837,14 @@
       <c r="K7" s="1" t="n">
         <v>250</v>
       </c>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>33006</v>
@@ -749,19 +853,22 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>180</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>500</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -769,7 +876,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>33007</v>
@@ -778,13 +885,13 @@
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>300</v>
@@ -792,13 +899,14 @@
       <c r="K9" s="1" t="n">
         <v>500</v>
       </c>
+      <c r="L9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>33008</v>
@@ -807,13 +915,13 @@
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J10" s="1" t="n">
         <v>420</v>
@@ -821,13 +929,14 @@
       <c r="K10" s="1" t="n">
         <v>500</v>
       </c>
+      <c r="L10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>33009</v>
@@ -839,13 +948,16 @@
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>180</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>750</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -853,19 +965,19 @@
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>33010</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>450</v>
@@ -873,13 +985,14 @@
       <c r="K12" s="1" t="n">
         <v>750</v>
       </c>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>33011</v>
@@ -891,13 +1004,16 @@
         <v>1</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>120</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>420</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -905,7 +1021,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>33012</v>
@@ -917,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J14" s="1" t="n">
         <v>120</v>
@@ -925,13 +1041,14 @@
       <c r="K14" s="1" t="n">
         <v>600</v>
       </c>
+      <c r="L14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>33013</v>
@@ -943,13 +1060,16 @@
         <v>1</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J15" s="1" t="n">
         <v>700</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>500</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -957,7 +1077,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>33014</v>
@@ -969,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J16" s="1" t="n">
         <v>700</v>
@@ -977,25 +1097,26 @@
       <c r="K16" s="1" t="n">
         <v>750</v>
       </c>
+      <c r="L16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>33015</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J17" s="1" t="n">
         <v>1050</v>
@@ -1003,13 +1124,14 @@
       <c r="K17" s="1" t="n">
         <v>500</v>
       </c>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>33016</v>
@@ -1021,7 +1143,7 @@
         <v>1</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J18" s="1" t="n">
         <v>1050</v>
@@ -1029,13 +1151,14 @@
       <c r="K18" s="1" t="n">
         <v>750</v>
       </c>
+      <c r="L18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>33017</v>
@@ -1047,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J19" s="1" t="n">
         <v>1200</v>
@@ -1055,13 +1178,14 @@
       <c r="K19" s="1" t="n">
         <v>600</v>
       </c>
+      <c r="L19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>33018</v>
@@ -1073,13 +1197,16 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J20" s="1" t="n">
         <v>1400</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>500</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1087,7 +1214,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>33019</v>
@@ -1098,8 +1225,8 @@
       <c r="H21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>53</v>
+      <c r="I21" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="J21" s="1" t="n">
         <v>1600</v>
@@ -1107,25 +1234,26 @@
       <c r="K21" s="1" t="n">
         <v>500</v>
       </c>
+      <c r="L21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>33020</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J22" s="1" t="n">
         <v>450</v>
@@ -1133,25 +1261,26 @@
       <c r="K22" s="1" t="n">
         <v>350</v>
       </c>
+      <c r="L22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>33021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="J23" s="1" t="n">
         <v>350</v>
@@ -1159,6 +1288,7 @@
       <c r="K23" s="1" t="n">
         <v>800</v>
       </c>
+      <c r="L23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="70">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -221,16 +221,13 @@
     <t xml:space="preserve">Value</t>
   </si>
   <si>
-    <t xml:space="preserve">VFX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ComboTransition</t>
+    <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
   </si>
   <si>
     <t xml:space="preserve">Stat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
@@ -300,7 +297,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,12 +331,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEE6EF"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8CB"/>
         <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
@@ -391,7 +382,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -460,10 +451,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +496,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFDDE8CB"/>
+      <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1447,7 +1434,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7.29"/>
@@ -1580,6 +1567,8 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
@@ -1603,8 +1592,8 @@
       <c r="C10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>69</v>
+      <c r="D10" s="14" t="s">
+        <v>67</v>
       </c>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
@@ -1673,8 +1662,8 @@
       <c r="C15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>70</v>
+      <c r="D15" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1687,8 +1676,8 @@
       <c r="C16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>70</v>
+      <c r="D16" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -228,6 +228,12 @@
   </si>
   <si>
     <t xml:space="preserve">Stat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddMovesetKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dash</t>
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
@@ -382,72 +388,76 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -635,7 +645,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M24"/>
-  <sheetFormatPr defaultColWidth="12.63671875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.6484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="17.63"/>
@@ -1440,8 +1450,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="22.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="18.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="7.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="7.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="7" width="12.67"/>
   </cols>
@@ -1567,8 +1577,8 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10"/>
@@ -1595,8 +1605,12 @@
       <c r="D10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="E10" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10"/>
@@ -1662,8 +1676,8 @@
       <c r="C15" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>69</v>
+      <c r="D15" s="17" t="s">
+        <v>71</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1676,8 +1690,8 @@
       <c r="C16" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>69</v>
+      <c r="D16" s="17" t="s">
+        <v>71</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -230,7 +230,10 @@
     <t xml:space="preserve">Stat</t>
   </si>
   <si>
-    <t xml:space="preserve">AddMovesetKey</t>
+    <t xml:space="preserve">AttackSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
     <t xml:space="preserve">Dash</t>
@@ -1575,8 +1578,12 @@
       <c r="D8" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
     </row>
@@ -1606,10 +1613,10 @@
         <v>67</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1677,7 +1684,7 @@
         <v>53</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1691,7 +1698,7 @@
         <v>55</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
+  <fileVersion appName="Calc" lowestEdited="7"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skill" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="SkillModifier" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -31,6 +32,9 @@
     <t xml:space="preserve">설명</t>
   </si>
   <si>
+    <t xml:space="preserve">SkillNameTid</t>
+  </si>
+  <si>
     <t xml:space="preserve">TextTid</t>
   </si>
   <si>
@@ -55,12 +59,18 @@
     <t xml:space="preserve">PositionY</t>
   </si>
   <si>
+    <t xml:space="preserve">VideoPathString</t>
+  </si>
+  <si>
     <t xml:space="preserve">일반 공격</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Normal-Attack-Icon-_1_.Img_Normal-Attack-Icon-_1_</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/Movies/TestVideo.TestVideo</t>
+  </si>
+  <si>
     <t xml:space="preserve">강공격</t>
   </si>
   <si>
@@ -200,6 +210,36 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApplyType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MovesetKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etc</t>
   </si>
 </sst>
 </file>
@@ -209,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="9"/>
       <name val="맑은 고딕 Semilight"/>
@@ -245,8 +285,28 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕 Semilight"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,14 +315,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.3499"/>
+        <fgColor theme="1" tint="0.3498"/>
         <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFCCCCFF"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFD7"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8CE"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEE6EF"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFDEE6EF"/>
       </patternFill>
     </fill>
   </fills>
@@ -307,12 +391,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -324,16 +408,60 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -365,12 +493,12 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFFFFD7"/>
+      <rgbColor rgb="FFDEE6EF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDDDDDD"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -386,7 +514,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFD8CE"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -519,19 +647,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr defaultColWidth="12.6484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.81"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.91"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="12.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="17.63"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.81"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12" min="10" style="1" width="12.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.18"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="14" style="1" width="12.64"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -565,8 +695,14 @@
       <c r="K1" s="2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L1" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M1" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -598,569 +734,701 @@
       <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="n">
+        <v>34001</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>33001</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
       <c r="H3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J3" s="1" t="n">
+      <c r="J3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="K3" s="1" t="n">
+      <c r="L3" s="1" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M3" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="4" t="n">
+        <v>34002</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>33002</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
       <c r="H4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="n">
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M4" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>34003</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>33003</v>
       </c>
-      <c r="G5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>900</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M5" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="n">
+        <v>34004</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>33004</v>
       </c>
-      <c r="G6" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>1200</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M6" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="n">
         <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="n">
+        <v>34005</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>33005</v>
       </c>
-      <c r="G7" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>1500</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>250</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M7" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="n">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>34006</v>
+      </c>
+      <c r="E8" s="1" t="n">
         <v>33006</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="1" t="n">
+      <c r="F8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M8" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="n">
+        <v>34007</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>33007</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="1" t="n">
+      <c r="F9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="L9" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M9" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="n">
         <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D10" s="4" t="n">
+        <v>34008</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>33008</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="1" t="n">
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>420</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M10" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="n">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>34009</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>33009</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="F11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="1" t="n">
+      <c r="I11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>180</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="L11" s="1" t="n">
         <v>750</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M11" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D12" s="4" t="n">
+        <v>34010</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>33010</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="1" t="n">
+      <c r="F12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>450</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="L12" s="1" t="n">
         <v>750</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M12" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D13" s="4" t="n">
+        <v>34011</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>33011</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="1" t="n">
+      <c r="F13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="1" t="n">
         <v>420</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M13" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>34012</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>33012</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="F14" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="1" t="n">
+      <c r="I14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="K14" s="1" t="n">
+      <c r="L14" s="1" t="n">
         <v>600</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M14" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="n">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D15" s="4" t="n">
+        <v>34013</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>33013</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="F15" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="1" t="n">
+      <c r="I15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="L15" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M15" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="n">
         <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D16" s="4" t="n">
+        <v>34014</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>33014</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="F16" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J16" s="1" t="n">
+      <c r="I16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="1" t="n">
         <v>700</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="L16" s="1" t="n">
         <v>750</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M16" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="n">
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>34015</v>
+      </c>
+      <c r="E17" s="1" t="n">
         <v>33015</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="1" t="n">
+      <c r="F17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K17" s="1" t="n">
         <v>1050</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M17" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D18" s="4" t="n">
+        <v>34016</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>33016</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" s="1" t="n">
+      <c r="F18" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K18" s="1" t="n">
         <v>1050</v>
       </c>
-      <c r="K18" s="1" t="n">
+      <c r="L18" s="1" t="n">
         <v>750</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M18" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D19" s="4" t="n">
+        <v>34017</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>33017</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="F19" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J19" s="1" t="n">
+      <c r="I19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="1" t="n">
         <v>1200</v>
       </c>
-      <c r="K19" s="1" t="n">
+      <c r="L19" s="1" t="n">
         <v>600</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M19" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>34018</v>
+      </c>
+      <c r="E20" s="1" t="n">
         <v>33018</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="F20" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" s="1" t="n">
+      <c r="I20" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="1" t="n">
         <v>1400</v>
       </c>
-      <c r="K20" s="1" t="n">
+      <c r="L20" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M20" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D21" s="4" t="n">
+        <v>34019</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>33019</v>
       </c>
-      <c r="E21" s="1" t="n">
+      <c r="F21" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J21" s="1" t="n">
+      <c r="I21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" s="1" t="n">
         <v>1600</v>
       </c>
-      <c r="K21" s="1" t="n">
+      <c r="L21" s="1" t="n">
         <v>500</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M21" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D22" s="4" t="n">
+        <v>34020</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>33020</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="J22" s="1" t="n">
+      <c r="F22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K22" s="1" t="n">
         <v>450</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="L22" s="1" t="n">
         <v>350</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M22" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="n">
         <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>34021</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>33021</v>
       </c>
-      <c r="E23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J23" s="1" t="n">
+      <c r="F23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" s="1" t="n">
         <v>350</v>
       </c>
-      <c r="K23" s="1" t="n">
+      <c r="L23" s="1" t="n">
         <v>800</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M23" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4"/>
     </row>
   </sheetData>
@@ -1172,4 +1440,304 @@
     <oddFooter>&amp;C&amp;"Times New Roman,보통"&amp;12페이지 &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="22.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="7.12"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="7" width="12.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10"/>
+      <c r="B7" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="10"/>
+      <c r="B16" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="10"/>
+      <c r="B17" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="10"/>
+      <c r="B18" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,보통"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,보통"&amp;12페이지 &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -221,6 +221,12 @@
     <t xml:space="preserve">Value</t>
   </si>
   <si>
+    <t xml:space="preserve">예상 결과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reset</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
@@ -233,10 +239,28 @@
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
     <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
     <t xml:space="preserve">Dash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxStamina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaRecovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가드 시 피해 감소율 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">기본값 0.5 * 1.5 = 0.75</t>
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
@@ -391,7 +415,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -421,7 +445,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -430,10 +454,6 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -457,7 +477,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1447,19 +1467,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="22.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="26.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="18.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="7.12"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="23.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="6.94"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="12.67"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1478,8 +1500,14 @@
       <c r="F1" s="8" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G1" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9"/>
       <c r="B2" s="9" t="s">
         <v>1</v>
@@ -1496,240 +1524,238 @@
       <c r="F2" s="9" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11" t="n">
+      <c r="G2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="n">
+      <c r="D3" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11" t="n">
+      <c r="D4" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11" t="n">
+      <c r="D5" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11" t="n">
+      <c r="D6" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11" t="n">
+      <c r="D7" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E8" s="10" t="s">
+      <c r="D8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10"/>
-      <c r="B9" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11" t="n">
+    </row>
+    <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11" t="n">
+      <c r="E12" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11" t="n">
+      <c r="D13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-    </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11" t="n">
+      <c r="C14" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-    </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11" t="n">
+      <c r="D15" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-    </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11" t="n">
+      <c r="D16" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11" t="n">
+      <c r="D17" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
+      <c r="D18" s="13" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -221,10 +221,10 @@
     <t xml:space="preserve">Value</t>
   </si>
   <si>
-    <t xml:space="preserve">예상 결과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset</t>
+    <t xml:space="preserve">결과</t>
+  </si>
+  <si>
+    <t xml:space="preserve">리셋</t>
   </si>
   <si>
     <t xml:space="preserve">Element</t>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -227,7 +227,19 @@
     <t xml:space="preserve">리셋</t>
   </si>
   <si>
+    <t xml:space="preserve">Value2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponNiagara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
   </si>
   <si>
     <t xml:space="preserve">Action</t>
@@ -284,16 +296,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -564,37 +579,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1506,6 +1521,9 @@
       <c r="H1" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="I1" s="8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9"/>
@@ -1530,6 +1548,9 @@
       <c r="H2" s="7" t="s">
         <v>67</v>
       </c>
+      <c r="I2" s="9" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="10" t="n">
@@ -1539,7 +1560,16 @@
         <v>24</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1550,7 +1580,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1561,7 +1594,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1572,7 +1605,7 @@
         <v>33</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1583,7 +1616,7 @@
         <v>35</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1594,16 +1627,16 @@
         <v>38</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -1616,7 +1649,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1627,16 +1660,16 @@
         <v>42</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1647,7 +1680,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1658,16 +1691,16 @@
         <v>46</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1678,16 +1711,16 @@
         <v>49</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1695,22 +1728,22 @@
         <v>17</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1721,7 +1754,7 @@
         <v>53</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1732,7 +1765,7 @@
         <v>55</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1743,7 +1776,7 @@
         <v>57</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1754,7 +1787,7 @@
         <v>60</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="86">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/Assets/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">/Game/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
@@ -1568,7 +1571,16 @@
       <c r="F3" s="7" t="s">
         <v>71</v>
       </c>
+      <c r="G3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="I3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1605,7 +1617,7 @@
         <v>33</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1616,7 +1628,7 @@
         <v>35</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1627,16 +1639,16 @@
         <v>38</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
@@ -1649,7 +1661,7 @@
         <v>40</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1660,16 +1672,16 @@
         <v>42</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1680,7 +1692,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1691,16 +1703,16 @@
         <v>46</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1711,16 +1723,16 @@
         <v>49</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" s="7" t="n">
         <v>1.2</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1728,22 +1740,22 @@
         <v>17</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>1.5</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1754,7 +1766,7 @@
         <v>53</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1765,7 +1777,7 @@
         <v>55</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1776,7 +1788,7 @@
         <v>57</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1787,7 +1799,7 @@
         <v>60</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="84">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -212,37 +212,34 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
   </si>
   <si>
+    <t xml:space="preserve">스킬 설명설명</t>
+  </si>
+  <si>
     <t xml:space="preserve">ApplyType</t>
   </si>
   <si>
     <t xml:space="preserve">Target</t>
   </si>
   <si>
+    <t xml:space="preserve">값 설명</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
   </si>
   <si>
-    <t xml:space="preserve">결과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">리셋</t>
-  </si>
-  <si>
     <t xml:space="preserve">Value2</t>
   </si>
   <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
-    <t xml:space="preserve">WeaponNiagara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Assets/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
+    <t xml:space="preserve">WeaponVFX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value: 무기 VFX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value2: 트레일 VFX</t>
   </si>
   <si>
     <t xml:space="preserve">Action</t>
@@ -254,12 +251,12 @@
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
-    <t xml:space="preserve">O</t>
-  </si>
-  <si>
     <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
+    <t xml:space="preserve">Moveset 키 추가</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dash</t>
   </si>
   <si>
@@ -273,9 +270,6 @@
   </si>
   <si>
     <t xml:space="preserve">Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본값 0.5 * 1.5 = 0.75</t>
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
@@ -348,7 +342,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -376,6 +370,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD8CE"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8CB"/>
         <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
@@ -433,7 +433,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -491,6 +491,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -498,7 +502,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -547,7 +551,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDDE8CB"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -1485,18 +1489,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="26.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="7.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="23.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="6.94"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="22.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="7" width="28.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="7" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1516,15 +1520,12 @@
         <v>1</v>
       </c>
       <c r="F1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H1" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I1" s="8" t="n">
+      <c r="G1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="8" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1534,24 +1535,21 @@
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1571,18 +1569,6 @@
       <c r="F3" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="n">
@@ -1597,6 +1583,9 @@
       <c r="E4" s="7" t="s">
         <v>70</v>
       </c>
+      <c r="F4" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="n">
@@ -1617,7 +1606,7 @@
         <v>33</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1628,30 +1617,26 @@
         <v>35</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+      <c r="I8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="n">
@@ -1661,27 +1646,27 @@
         <v>40</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="14" t="s">
         <v>42</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1692,70 +1677,58 @@
         <v>44</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>75</v>
+      <c r="D12" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="7" t="n">
+        <v>79</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>1.2</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>75</v>
+      <c r="D13" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>1.2</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D14" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>1.5</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1765,8 +1738,8 @@
       <c r="C15" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>85</v>
+      <c r="D15" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1776,8 +1749,8 @@
       <c r="C16" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>85</v>
+      <c r="D16" s="17" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1788,7 +1761,7 @@
         <v>57</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1799,7 +1772,7 @@
         <v>60</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="91">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -239,7 +239,28 @@
     <t xml:space="preserve">Value: 무기 VFX</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
     <t xml:space="preserve">Value2: 트레일 VFX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/Sword/NS_Sword_Ice.NS_Sword_Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Ice.NS_SlashTrail_Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V3/NS_StylizedWeapon_V3_09.NS_StylizedWeapon_V3_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_12.NS_Trail_12</t>
   </si>
   <si>
     <t xml:space="preserve">Action</t>
@@ -363,6 +384,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8CB"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFD7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
@@ -370,12 +397,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD8CE"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDE8CB"/>
         <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
@@ -433,7 +454,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -466,32 +487,48 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1497,282 +1534,315 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="22.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="22.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="7" width="28.07"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="7" width="12.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="7" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="n">
+      <c r="B1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="n">
+      <c r="D1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="G1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="n">
+      <c r="G1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="9" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="15" t="s">
         <v>69</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>71</v>
       </c>
+      <c r="G3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="15" t="s">
         <v>69</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>72</v>
+      <c r="F4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="15" t="s">
         <v>69</v>
       </c>
+      <c r="E5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>73</v>
+      <c r="D6" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>73</v>
+      <c r="D7" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="13" t="n">
         <v>11</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="15" t="s">
-        <v>74</v>
+      <c r="D8" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="16"/>
+      <c r="I8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>73</v>
+      <c r="D9" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="13" t="n">
         <v>13</v>
       </c>
       <c r="C10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>73</v>
+      <c r="D10" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>77</v>
+        <v>83</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>73</v>
+      <c r="D11" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="n">
+      <c r="B12" s="13" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="15" t="s">
-        <v>74</v>
+      <c r="D12" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="13" t="n">
         <v>16</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>74</v>
+      <c r="D13" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="13" t="n">
         <v>17</v>
       </c>
       <c r="C14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="15" t="s">
-        <v>74</v>
-      </c>
       <c r="E14" s="7" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>83</v>
+      <c r="D15" s="21" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>83</v>
+      <c r="D16" s="21" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>73</v>
+      <c r="D17" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="13" t="n">
         <v>21</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>73</v>
+      <c r="D18" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="91">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -212,24 +212,57 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
   </si>
   <si>
+    <t xml:space="preserve">스킬 설명설명</t>
+  </si>
+  <si>
     <t xml:space="preserve">ApplyType</t>
   </si>
   <si>
     <t xml:space="preserve">Target</t>
   </si>
   <si>
+    <t xml:space="preserve">값 설명</t>
+  </si>
+  <si>
     <t xml:space="preserve">Value</t>
   </si>
   <si>
-    <t xml:space="preserve">예상 결과</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reset</t>
+    <t xml:space="preserve">Value2</t>
   </si>
   <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
+    <t xml:space="preserve">WeaponVFX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value: 무기 VFX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value2: 트레일 VFX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/Sword/NS_Sword_Ice.NS_Sword_Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Ice.NS_SlashTrail_Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V3/NS_StylizedWeapon_V3_09.NS_StylizedWeapon_V3_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_12.NS_Trail_12</t>
+  </si>
+  <si>
     <t xml:space="preserve">Action</t>
   </si>
   <si>
@@ -239,12 +272,12 @@
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
-    <t xml:space="preserve">O</t>
-  </si>
-  <si>
     <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
+    <t xml:space="preserve">Moveset 키 추가</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dash</t>
   </si>
   <si>
@@ -258,9 +291,6 @@
   </si>
   <si>
     <t xml:space="preserve">Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">기본값 0.5 * 1.5 = 0.75</t>
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
@@ -284,16 +314,19 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -330,7 +363,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,6 +379,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
+        <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE8CB"/>
         <bgColor rgb="FFDDDDDD"/>
       </patternFill>
     </fill>
@@ -415,7 +454,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -448,39 +487,59 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -529,7 +588,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFDDE8CB"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -564,37 +623,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1467,294 +1526,323 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="26.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="7.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="7" width="23.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="7" width="6.94"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="8.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="22.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="7" width="28.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="7" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="n">
+      <c r="B1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G1" s="7" t="n">
+      <c r="D1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H1" s="7" t="n">
-        <v>0</v>
+      <c r="G1" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="G2" s="11" t="s">
         <v>67</v>
       </c>
+      <c r="H2" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>68</v>
+      <c r="D3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>68</v>
+      <c r="D4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>68</v>
+      <c r="D5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="13" t="s">
-        <v>69</v>
+      <c r="D6" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>69</v>
+      <c r="D7" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>70</v>
+      <c r="D8" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="7" t="n">
+        <v>82</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+      <c r="I8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="13" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>69</v>
+      <c r="D9" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="13" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>69</v>
+      <c r="D10" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>72</v>
+        <v>83</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="13" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>69</v>
+      <c r="D11" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>70</v>
+      <c r="D12" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="7" t="n">
+        <v>86</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="14" t="s">
-        <v>70</v>
+      <c r="D13" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="7" t="n">
+        <v>87</v>
+      </c>
+      <c r="G13" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10" t="n">
+      <c r="B14" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>70</v>
+      <c r="C14" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>81</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>1.5</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="18" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="D16" s="16" t="s">
+    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="97">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -230,6 +230,9 @@
     <t xml:space="preserve">Value2</t>
   </si>
   <si>
+    <t xml:space="preserve">Value3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
@@ -294,6 +297,21 @@
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ComboOverride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value: 이전 콤보 Tid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeavyAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value2: 입력 커맨드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value3: 다음 콤보 Tid</t>
   </si>
 </sst>
 </file>
@@ -454,7 +472,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -487,10 +505,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -519,7 +533,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1526,7 +1540,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.78"/>
@@ -1534,315 +1548,348 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="22.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="7" width="28.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="22.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="7" width="28.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="10" style="7" width="12.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="7" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="n">
+      <c r="B1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="10" t="n">
+      <c r="D1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="9" t="n">
+      <c r="G1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>68</v>
       </c>
+      <c r="I2" s="10" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>69</v>
+      <c r="D3" s="14" t="s">
+        <v>70</v>
       </c>
       <c r="E3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>74</v>
-      </c>
       <c r="G5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>80</v>
-      </c>
+      <c r="D6" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>80</v>
-      </c>
+      <c r="D7" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="0"/>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>81</v>
+      <c r="D8" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1.2</v>
       </c>
-      <c r="I8" s="20"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>80</v>
+      <c r="D9" s="17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>80</v>
+      <c r="D10" s="17" t="s">
+        <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="8" t="s">
         <v>84</v>
       </c>
+      <c r="F10" s="7" t="s">
+        <v>85</v>
+      </c>
       <c r="G10" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>80</v>
+      <c r="D11" s="17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>81</v>
+      <c r="D12" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>81</v>
+      <c r="D13" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>81</v>
+      <c r="C14" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>90</v>
+      <c r="D15" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>90</v>
+      <c r="D16" s="20" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="17" t="s">
+      <c r="C17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="18" t="s">
-        <v>80</v>
+      <c r="D17" s="17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>80</v>
+      <c r="D18" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>73001</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F20" s="7" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="98">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -275,6 +275,15 @@
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">LRR 커맨드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ComboOverride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeavyAttack</t>
+  </si>
+  <si>
     <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
@@ -299,13 +308,7 @@
     <t xml:space="preserve">Etc</t>
   </si>
   <si>
-    <t xml:space="preserve">ComboOverride</t>
-  </si>
-  <si>
     <t xml:space="preserve">Value: 이전 콤보 Tid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HeavyAttack</t>
   </si>
   <si>
     <t xml:space="preserve">Value2: 입력 커맨드</t>
@@ -1726,7 +1729,7 @@
         <v>83</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I8" s="19"/>
     </row>
@@ -1734,11 +1737,23 @@
       <c r="B9" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="16" t="s">
-        <v>40</v>
+      <c r="C9" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>81</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>71001</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>72011</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1752,13 +1767,13 @@
         <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1783,7 +1798,7 @@
         <v>82</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
@@ -1800,7 +1815,7 @@
         <v>82</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
@@ -1811,13 +1826,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>82</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
@@ -1831,7 +1846,7 @@
         <v>53</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1842,7 +1857,7 @@
         <v>55</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1860,23 +1875,23 @@
       <c r="B18" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="13" t="s">
         <v>60</v>
       </c>
       <c r="D18" s="17" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>73001</v>
@@ -1884,12 +1899,12 @@
     </row>
     <row r="19" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F19" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F20" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="100">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -269,43 +269,49 @@
     <t xml:space="preserve">Action</t>
   </si>
   <si>
+    <t xml:space="preserve">ComboOverride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeavyAttack</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stat</t>
   </si>
   <si>
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">기본공격 4타 대체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LightAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MovesetKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moveset 키 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxStamina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StaminaRecovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가드 시 피해 감소율 증가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etc</t>
+  </si>
+  <si>
     <t xml:space="preserve">LRR 커맨드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ComboOverride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HeavyAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MovesetKey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moveset 키 추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxStamina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StaminaRecovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가드 시 피해 감소율 증가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etc</t>
   </si>
   <si>
     <t xml:space="preserve">Value: 이전 콤보 Tid</t>
@@ -335,19 +341,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -475,7 +478,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -537,10 +540,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -552,7 +551,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -640,37 +639,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1658,7 +1657,7 @@
       <c r="G4" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="7" t="s">
         <v>78</v>
       </c>
       <c r="I4" s="7" t="s">
@@ -1695,25 +1694,35 @@
       <c r="B6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F7" s="0"/>
+      <c r="E7" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>72004</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="n">
@@ -1722,38 +1731,37 @@
       <c r="C8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>82</v>
+      <c r="D8" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1.1</v>
       </c>
-      <c r="I8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="12" t="n">
         <v>12</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>81</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>71001</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>72011</v>
+        <v>82</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>71003</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>71011</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1763,27 +1771,27 @@
       <c r="C10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1794,11 +1802,11 @@
       <c r="C12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="18" t="s">
-        <v>82</v>
+      <c r="D12" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
@@ -1811,11 +1819,11 @@
       <c r="C13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>82</v>
+      <c r="D13" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
@@ -1826,13 +1834,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>82</v>
+        <v>93</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>84</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
@@ -1842,33 +1850,48 @@
       <c r="B15" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>94</v>
+      <c r="D15" s="19" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>94</v>
+      <c r="D16" s="19" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="17" t="s">
+      <c r="C17" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>81</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>71001</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>72011</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1878,20 +1901,20 @@
       <c r="C18" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="16" t="s">
         <v>81</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>73001</v>
@@ -1899,13 +1922,11 @@
     </row>
     <row r="19" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F19" s="7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F20" s="7" t="s">
-        <v>97</v>
-      </c>
+      <c r="F20" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="101">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">스킬 설명설명</t>
+    <t xml:space="preserve">스킬 설명</t>
   </si>
   <si>
     <t xml:space="preserve">ApplyType</t>
@@ -233,6 +233,9 @@
     <t xml:space="preserve">Value3</t>
   </si>
   <si>
+    <t xml:space="preserve">Value4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
@@ -245,10 +248,7 @@
     <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Fire.NS_SlashTrail_Fire</t>
   </si>
   <si>
     <t xml:space="preserve">Value2: 트레일 VFX</t>
@@ -260,10 +260,13 @@
     <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Ice.NS_SlashTrail_Ice</t>
   </si>
   <si>
+    <t xml:space="preserve"> Value3: 트레일 VFX Z방향 오프셋, Value4: 트레일 스케일</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V3/NS_StylizedWeapon_V3_09.NS_StylizedWeapon_V3_09</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_12.NS_Trail_12</t>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Electric.NS_SlashTrail_Electric</t>
   </si>
   <si>
     <t xml:space="preserve">Action</t>
@@ -551,12 +554,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1542,7 +1545,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.78"/>
@@ -1550,7 +1553,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="22.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="34.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="7" width="28.07"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="10" style="7" width="12.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="7" width="12.67"/>
@@ -1584,6 +1587,9 @@
       <c r="I1" s="8" t="n">
         <v>1</v>
       </c>
+      <c r="J1" s="8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10"/>
@@ -1611,6 +1617,9 @@
       <c r="I2" s="10" t="s">
         <v>69</v>
       </c>
+      <c r="J2" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="12" t="n">
@@ -1620,22 +1629,25 @@
         <v>24</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="7" t="s">
         <v>75</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1646,10 +1658,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>76</v>
@@ -1660,8 +1672,11 @@
       <c r="H4" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>75</v>
+      <c r="I4" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1672,22 +1687,25 @@
         <v>30</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>75</v>
+      <c r="H5" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1698,7 +1716,7 @@
         <v>33</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1709,16 +1727,16 @@
         <v>35</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>72004</v>
@@ -1732,10 +1750,10 @@
         <v>38</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1.1</v>
@@ -1746,21 +1764,21 @@
         <v>12</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="18" t="n">
+        <v>83</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <v>71003</v>
       </c>
-      <c r="H9" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="I9" s="18" t="n">
+      <c r="H9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="7" t="n">
         <v>71011</v>
       </c>
     </row>
@@ -1772,16 +1790,16 @@
         <v>42</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1792,7 +1810,7 @@
         <v>44</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1803,10 +1821,10 @@
         <v>46</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
@@ -1820,10 +1838,10 @@
         <v>49</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
@@ -1834,13 +1852,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
@@ -1853,8 +1871,8 @@
       <c r="C15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>95</v>
+      <c r="D15" s="18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1864,8 +1882,8 @@
       <c r="C16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>95</v>
+      <c r="D16" s="18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1873,22 +1891,22 @@
         <v>20</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>71001</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>72011</v>
@@ -1902,19 +1920,19 @@
         <v>60</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>73001</v>
@@ -1922,11 +1940,11 @@
     </row>
     <row r="19" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F19" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F20" s="0"/>
+      <c r="F20" s="19"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="101">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
   </si>
   <si>
-    <t xml:space="preserve">스킬 설명설명</t>
+    <t xml:space="preserve">스킬 설명</t>
   </si>
   <si>
     <t xml:space="preserve">ApplyType</t>
@@ -230,6 +230,12 @@
     <t xml:space="preserve">Value2</t>
   </si>
   <si>
+    <t xml:space="preserve">Value3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Element</t>
   </si>
   <si>
@@ -242,10 +248,7 @@
     <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V4/NS_StylizedWeapon_V4_05.NS_StylizedWeapon_V4_05</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_03.NS_Trail_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Fire.NS_SlashTrail_Fire</t>
   </si>
   <si>
     <t xml:space="preserve">Value2: 트레일 VFX</t>
@@ -257,21 +260,36 @@
     <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Ice.NS_SlashTrail_Ice</t>
   </si>
   <si>
+    <t xml:space="preserve"> Value3: 트레일 VFX Z방향 오프셋, Value4: 트레일 스케일</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/Assets/WeaponVFX/Weapon/MeleeWeaponAura_VFX/VFX/V3/NS_StylizedWeapon_V3_09.NS_StylizedWeapon_V3_09</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SwordTrailVFX/VFX/NS_Trail_12.NS_Trail_12</t>
+    <t xml:space="preserve">/Game/Assets/WeaponVFX/Trail/SlashTrailElemental/Niagara/SlashTrail/NS_SlashTrail_Electric.NS_SlashTrail_Electric</t>
   </si>
   <si>
     <t xml:space="preserve">Action</t>
   </si>
   <si>
+    <t xml:space="preserve">ComboOverride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeavyAttack</t>
+  </si>
+  <si>
     <t xml:space="preserve">Stat</t>
   </si>
   <si>
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">기본공격 4타 대체</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LightAttack</t>
+  </si>
+  <si>
     <t xml:space="preserve">MovesetKey</t>
   </si>
   <si>
@@ -294,6 +312,18 @@
   </si>
   <si>
     <t xml:space="preserve">Etc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRR 커맨드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value: 이전 콤보 Tid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value2: 입력 커맨드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value3: 다음 콤보 Tid</t>
   </si>
 </sst>
 </file>
@@ -314,19 +344,16 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
     </font>
     <font>
       <sz val="9"/>
@@ -454,7 +481,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -487,10 +514,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -519,10 +542,6 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -535,12 +554,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -623,37 +642,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1526,7 +1545,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="12.67578125" defaultRowHeight="16.65" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.78"/>
@@ -1534,316 +1553,398 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="25.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="11.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="17.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="22.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="7" width="28.07"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="9" style="7" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="34.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="7" width="28.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="10" style="7" width="12.67"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="7" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="n">
+      <c r="B1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F1" s="10" t="n">
+      <c r="D1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="G1" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H1" s="9" t="n">
+      <c r="G1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="10" t="s">
         <v>68</v>
       </c>
+      <c r="I2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>69</v>
+      <c r="D3" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F3" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" s="7" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>75</v>
+      <c r="F4" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>74</v>
+      <c r="H4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>69</v>
+      <c r="D5" s="14" t="s">
+        <v>71</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>74</v>
+        <v>80</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="18" t="s">
-        <v>80</v>
+      <c r="D6" s="16" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="18" t="s">
-        <v>80</v>
+      <c r="D7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>72004</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>81</v>
+      <c r="D8" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>80</v>
+      <c r="E9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>71003</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>71011</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>80</v>
+      <c r="D10" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="G10" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="17" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>81</v>
-      </c>
       <c r="E12" s="7" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>81</v>
+      <c r="D13" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>81</v>
+      <c r="C14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>90</v>
+      <c r="D15" s="18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="17" t="s">
+      <c r="C16" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="21" t="s">
-        <v>90</v>
+      <c r="D16" s="18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>80</v>
+      <c r="C17" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>71001</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>72011</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="C18" s="17" t="s">
+      <c r="C18" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>80</v>
-      </c>
+      <c r="D18" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>73001</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F20" s="19"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -542,6 +542,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -556,10 +560,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1644,7 +1644,7 @@
         <v>75</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>0.8</v>
@@ -1698,11 +1698,11 @@
       <c r="G5" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="15" t="s">
         <v>81</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="J5" s="7" t="n">
         <v>0.8</v>
@@ -1712,12 +1712,13 @@
       <c r="B6" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>82</v>
       </c>
+      <c r="F6" s="0"/>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="n">
@@ -1726,12 +1727,13 @@
       <c r="C7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>83</v>
       </c>
+      <c r="F7" s="0"/>
       <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
@@ -1749,7 +1751,7 @@
       <c r="C8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="18" t="s">
         <v>85</v>
       </c>
       <c r="E8" s="7" t="s">
@@ -1766,7 +1768,7 @@
       <c r="C9" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E9" s="7" t="s">
@@ -1789,7 +1791,7 @@
       <c r="C10" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
@@ -1806,10 +1808,10 @@
       <c r="B11" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="17" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1820,7 +1822,7 @@
       <c r="C12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>85</v>
       </c>
       <c r="E12" s="7" t="s">
@@ -1837,7 +1839,7 @@
       <c r="C13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>85</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -1854,7 +1856,7 @@
       <c r="C14" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>85</v>
       </c>
       <c r="E14" s="7" t="s">
@@ -1868,10 +1870,10 @@
       <c r="B15" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="19" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1879,10 +1881,10 @@
       <c r="B16" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="19" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1893,7 +1895,7 @@
       <c r="C17" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E17" s="7" t="s">
@@ -1919,7 +1921,7 @@
       <c r="C18" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="17" t="s">
         <v>82</v>
       </c>
       <c r="E18" s="7" t="s">
@@ -1944,7 +1946,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="F20" s="19"/>
+      <c r="F20" s="15"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="104">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -284,6 +284,9 @@
     <t xml:space="preserve">AttackSpeed</t>
   </si>
   <si>
+    <t xml:space="preserve">곱셈</t>
+  </si>
+  <si>
     <t xml:space="preserve">기본공격 4타 대체</t>
   </si>
   <si>
@@ -311,7 +314,13 @@
     <t xml:space="preserve">Guard</t>
   </si>
   <si>
-    <t xml:space="preserve">Etc</t>
+    <t xml:space="preserve">HealCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덧셈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HealAmount</t>
   </si>
   <si>
     <t xml:space="preserve">LRR 커맨드</t>
@@ -390,7 +399,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -406,13 +415,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
-        <bgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE8CB"/>
-        <bgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFDEE6EF"/>
       </patternFill>
     </fill>
     <fill>
@@ -424,19 +433,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD8CE"/>
-        <bgColor rgb="FFDDDDDD"/>
+        <bgColor rgb="FFDDE8CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEE6EF"/>
-        <bgColor rgb="FFDDDDDD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDDDDD"/>
-        <bgColor rgb="FFDEE6EF"/>
+        <bgColor rgb="FFDDE8CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -554,11 +557,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -596,7 +599,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -1718,7 +1721,7 @@
       <c r="D6" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F6" s="0"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="n">
@@ -1733,7 +1736,7 @@
       <c r="E7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="0"/>
+      <c r="F7" s="18"/>
       <c r="G7" s="7" t="n">
         <v>0</v>
       </c>
@@ -1751,11 +1754,14 @@
       <c r="C8" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>85</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>86</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1.1</v>
@@ -1766,7 +1772,7 @@
         <v>12</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="17" t="s">
         <v>82</v>
@@ -1778,7 +1784,7 @@
         <v>71003</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>71011</v>
@@ -1795,13 +1801,13 @@
         <v>82</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1822,11 +1828,14 @@
       <c r="C12" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>85</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>1.2</v>
@@ -1839,11 +1848,14 @@
       <c r="C13" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>85</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="G13" s="7" t="n">
         <v>1.2</v>
@@ -1854,13 +1866,16 @@
         <v>17</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>85</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1.5</v>
@@ -1874,7 +1889,16 @@
         <v>53</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1885,7 +1909,16 @@
         <v>55</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>96</v>
+        <v>85</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1893,7 +1926,7 @@
         <v>20</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D17" s="17" t="s">
         <v>82</v>
@@ -1902,7 +1935,7 @@
         <v>83</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>71001</v>
@@ -1928,7 +1961,7 @@
         <v>83</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
@@ -1942,7 +1975,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F19" s="7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -1885,7 +1885,7 @@
       <c r="B15" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="13" t="s">
         <v>53</v>
       </c>
       <c r="D15" s="19" t="s">
@@ -1905,7 +1905,7 @@
       <c r="B16" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="13" t="s">
         <v>55</v>
       </c>
       <c r="D16" s="19" t="s">

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="118">
   <si>
     <t xml:space="preserve">Client</t>
   </si>
@@ -68,69 +68,90 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Normal-Attack-Icon-_1_.Img_Normal-Attack-Icon-_1_</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/Movies/LightAttack.LightAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">강공격</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Heavy-Attack-Icon-_2_.Img_Heavy-Attack-Icon-_2_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/HeavyAttack.HeavyAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회피</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Dodge-Icon-_3_.Img_Dodge-Icon-_3_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/Roll.Roll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가드</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Guard-Icon-_4_.Img_Guard-Icon-_4_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/Guard.Guard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복 물약</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Greater-Potion-_5_.Img_Greater-Potion-_5_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/Heal.Heal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">불 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_fire-enchant-_6_.Img_fire-enchant-_6_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/Fire.Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">얼음 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_ice-enchant-_7_.Img_ice-enchant-_7_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/Ice.Ice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전격 속성 강화</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_No-enchant-_8_.Img_No-enchant-_8_</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/Electric.Electric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">특수공격 추가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Homing-Burst-_9_.Img_Homing-Burst-_9_</t>
+  </si>
+  <si>
     <t xml:space="preserve">/Game/Movies/SkillTest.SkillTest</t>
   </si>
   <si>
-    <t xml:space="preserve">강공격</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Heavy-Attack-Icon-_2_.Img_Heavy-Attack-Icon-_2_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회피</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Dodge-Icon-_3_.Img_Dodge-Icon-_3_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/Movies/Test1.Test1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가드</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Guard-Icon-_4_.Img_Guard-Icon-_4_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회복 물약</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Greater-Potion-_5_.Img_Greater-Potion-_5_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">불 속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_fire-enchant-_6_.Img_fire-enchant-_6_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">얼음 속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_ice-enchant-_7_.Img_ice-enchant-_7_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전격 속성 강화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_No-enchant-_8_.Img_No-enchant-_8_</t>
-  </si>
-  <si>
-    <t xml:space="preserve">특수공격 추가</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Homing-Burst-_9_.Img_Homing-Burst-_9_</t>
-  </si>
-  <si>
     <t xml:space="preserve">강공격 강화</t>
   </si>
   <si>
@@ -140,6 +161,9 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_enhanced-heavy-attack-_10_.Img_enhanced-heavy-attack-_10_</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/Movies/HeavyAttackUpgrade.HeavyAttackUpgrade</t>
+  </si>
+  <si>
     <t xml:space="preserve">공격속도 증가</t>
   </si>
   <si>
@@ -152,13 +176,16 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Final-Strike_Icon-_12_.Img_Final-Strike_Icon-_12_</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/Movies/LastLightAttackUpgrade.LastLightAttackUpgrade</t>
+  </si>
+  <si>
     <t xml:space="preserve">대시</t>
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Invincible-Dash-_13_.Img_Invincible-Dash-_13_</t>
   </si>
   <si>
-    <t xml:space="preserve">/Game/Movies/Test2.Test2</t>
+    <t xml:space="preserve">/Game/Movies/Dash.Dash</t>
   </si>
   <si>
     <t xml:space="preserve">대시 연계 공격</t>
@@ -209,6 +236,9 @@
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_normal-attack+-heavy-attack.Img_normal-attack+-heavy-attack</t>
   </si>
   <si>
+    <t xml:space="preserve">/Game/Movies/LRR.LRR</t>
+  </si>
+  <si>
     <t xml:space="preserve">차징 공격</t>
   </si>
   <si>
@@ -216,6 +246,9 @@
   </si>
   <si>
     <t xml:space="preserve">/Game/UI/SkillTree/Skill_Icon/Img_Charged-Attack.Img_Charged-Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/Game/Movies/ChargeAttack.ChargeAttack</t>
   </si>
   <si>
     <t xml:space="preserve">스킬 설명</t>
@@ -527,7 +560,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -539,7 +572,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="true"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -927,7 +960,7 @@
         <v>250</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -935,7 +968,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>34003</v>
@@ -950,7 +983,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="1" t="n">
         <v>900</v>
@@ -959,7 +992,7 @@
         <v>250</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -967,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>34004</v>
@@ -982,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" s="1" t="n">
         <v>1200</v>
@@ -991,7 +1024,7 @@
         <v>250</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -999,7 +1032,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>34005</v>
@@ -1014,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K7" s="1" t="n">
         <v>1500</v>
@@ -1023,7 +1056,7 @@
         <v>250</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1031,7 +1064,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>34006</v>
@@ -1043,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1" t="n">
         <v>180</v>
@@ -1058,7 +1091,7 @@
         <v>500</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1066,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>34007</v>
@@ -1078,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I9" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>300</v>
@@ -1093,7 +1126,7 @@
         <v>500</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1101,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>34008</v>
@@ -1113,13 +1146,13 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K10" s="1" t="n">
         <v>420</v>
@@ -1128,7 +1161,7 @@
         <v>500</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1136,7 +1169,7 @@
         <v>9</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>34009</v>
@@ -1151,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K11" s="1" t="n">
         <v>180</v>
@@ -1160,7 +1193,7 @@
         <v>750</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1168,7 +1201,7 @@
         <v>10</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>34010</v>
@@ -1177,13 +1210,13 @@
         <v>33010</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I12" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K12" s="1" t="n">
         <v>450</v>
@@ -1192,7 +1225,7 @@
         <v>750</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1200,7 +1233,7 @@
         <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>34011</v>
@@ -1215,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K13" s="1" t="n">
         <v>120</v>
@@ -1223,16 +1256,14 @@
       <c r="L13" s="1" t="n">
         <v>420</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="M13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>34012</v>
@@ -1247,7 +1278,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K14" s="1" t="n">
         <v>120</v>
@@ -1256,7 +1287,7 @@
         <v>600</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1264,7 +1295,7 @@
         <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>34013</v>
@@ -1279,7 +1310,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="K15" s="1" t="n">
         <v>700</v>
@@ -1288,7 +1319,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1296,7 +1327,7 @@
         <v>14</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>34014</v>
@@ -1311,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K16" s="1" t="n">
         <v>700</v>
@@ -1320,7 +1351,7 @@
         <v>750</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1328,7 +1359,7 @@
         <v>15</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>34015</v>
@@ -1337,13 +1368,13 @@
         <v>33015</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="I17" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K17" s="1" t="n">
         <v>1050</v>
@@ -1351,16 +1382,14 @@
       <c r="L17" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="M17" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="M17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="n">
         <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>34016</v>
@@ -1375,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K18" s="1" t="n">
         <v>1050</v>
@@ -1383,16 +1412,14 @@
       <c r="L18" s="1" t="n">
         <v>750</v>
       </c>
-      <c r="M18" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="M18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>34017</v>
@@ -1407,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="K19" s="1" t="n">
         <v>1200</v>
@@ -1415,16 +1442,14 @@
       <c r="L19" s="1" t="n">
         <v>600</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="M19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="n">
         <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D20" s="4" t="n">
         <v>34018</v>
@@ -1439,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K20" s="1" t="n">
         <v>1400</v>
@@ -1447,16 +1472,14 @@
       <c r="L20" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="M20" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="M20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4" t="n">
         <v>34019</v>
@@ -1471,7 +1494,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="K21" s="1" t="n">
         <v>1600</v>
@@ -1479,16 +1502,14 @@
       <c r="L21" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="M21" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>34020</v>
@@ -1497,13 +1518,13 @@
         <v>33020</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I22" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K22" s="1" t="n">
         <v>450</v>
@@ -1512,7 +1533,7 @@
         <v>350</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1520,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D23" s="4" t="n">
         <v>34021</v>
@@ -1529,22 +1550,22 @@
         <v>33021</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I23" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="L23" s="1" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1566,7 +1587,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultColWidth="12.6484375" defaultRowHeight="16.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="6.81"/>
@@ -1618,28 +1639,28 @@
         <v>1</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1647,22 +1668,22 @@
         <v>6</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I3" s="9" t="n">
         <v>160</v>
@@ -1676,22 +1697,22 @@
         <v>7</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="I4" s="9" t="n">
         <v>80</v>
@@ -1705,22 +1726,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>160</v>
@@ -1734,10 +1755,10 @@
         <v>9</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1745,19 +1766,19 @@
         <v>10</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>72004</v>
@@ -1768,16 +1789,16 @@
         <v>11</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>1.1</v>
@@ -1788,19 +1809,19 @@
         <v>12</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>71003</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>71011</v>
@@ -1811,19 +1832,19 @@
         <v>13</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1831,10 +1852,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1842,16 +1863,16 @@
         <v>15</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>1.2</v>
@@ -1862,16 +1883,16 @@
         <v>16</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>1.2</v>
@@ -1882,16 +1903,16 @@
         <v>17</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>1.5</v>
@@ -1903,16 +1924,16 @@
         <v>18</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>2</v>
@@ -1925,9 +1946,6 @@
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="9"/>
-      <c r="P15" s="0"/>
-      <c r="Q15" s="0"/>
-      <c r="R15" s="0"/>
     </row>
     <row r="16" s="18" customFormat="true" ht="16.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
@@ -1935,16 +1953,16 @@
         <v>19</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>25</v>
@@ -1957,31 +1975,28 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="9"/>
-      <c r="P16" s="0"/>
-      <c r="Q16" s="0"/>
-      <c r="R16" s="0"/>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="n">
         <v>20</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>71001</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>72011</v>
@@ -1992,22 +2007,22 @@
         <v>21</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I18" s="9" t="n">
         <v>73001</v>
@@ -2015,7 +2030,7 @@
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="F19" s="9" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/BADesign/Excel/SkillTree.xlsx
+++ b/BADesign/Excel/SkillTree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ProjectBA\BADesign\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B68633-B2A1-4404-85C4-900AEC3F10F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9C8ADE-7BBA-49C3-B9F7-C421F84FA102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="62295" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="101">
   <si>
     <t>Client</t>
   </si>
@@ -329,14 +329,6 @@
   </si>
   <si>
     <t>/Game/Movies/SkillTest.SkillTest</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Movies/Test1.Test1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>/Game/Movies/Test2.Test2</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -907,7 +899,7 @@
         <v>250</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.5">
@@ -1236,7 +1228,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.5">
